--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487605_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487605_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.4699</v>
+        <v>10.2644</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0875</v>
+        <v>6.509</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3823</v>
+        <v>3.7555</v>
       </c>
       <c r="G2" t="n">
         <v>5.0732</v>
@@ -610,13 +610,13 @@
         <v>2.7164</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.2745</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.2719</v>
+        <v>-0.8505</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2028</v>
+        <v>0.576</v>
       </c>
       <c r="V2" t="n">
         <v>3.7194</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. VICENTE VIANA</t>
+          <t>C. UNANUE CEGARRA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8786</v>
+        <v>4.1254</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4514</v>
+        <v>2.0329</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4271</v>
+        <v>2.0925</v>
       </c>
       <c r="G3" t="n">
-        <v>4.203</v>
+        <v>-0.1081</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8044</v>
+        <v>1.731</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3986</v>
+        <v>-1.8391</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5922</v>
+        <v>0.7578</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3892</v>
+        <v>3.242</v>
       </c>
       <c r="L3" t="n">
-        <v>0.203</v>
+        <v>-2.4841</v>
       </c>
       <c r="M3" t="n">
-        <v>1.6108</v>
+        <v>-0.866</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4152</v>
+        <v>-1.511</v>
       </c>
       <c r="O3" t="n">
-        <v>1.1956</v>
+        <v>0.645</v>
       </c>
       <c r="P3" t="n">
         <v>0.5821</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5523</v>
+        <v>2.5224</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5994</v>
+        <v>-0.6798999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5473</v>
+        <v>-0.4562</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0521</v>
+        <v>-0.2237</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.506</v>
+        <v>4.3313</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2821</v>
+        <v>3.6716</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.788</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. UNANUE CEGARRA</t>
+          <t>A. VICENTE VIANA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.992</v>
+        <v>3.1171</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4719</v>
+        <v>1.7718</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5201</v>
+        <v>1.3454</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1081</v>
+        <v>4.203</v>
       </c>
       <c r="H4" t="n">
-        <v>1.731</v>
+        <v>2.8044</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.8391</v>
+        <v>1.3986</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7578</v>
+        <v>2.5922</v>
       </c>
       <c r="K4" t="n">
-        <v>3.242</v>
+        <v>2.3892</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.4841</v>
+        <v>0.203</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.866</v>
+        <v>1.6108</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.511</v>
+        <v>0.4152</v>
       </c>
       <c r="O4" t="n">
-        <v>0.645</v>
+        <v>1.1956</v>
       </c>
       <c r="P4" t="n">
         <v>0.5821</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5224</v>
+        <v>1.5523</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.8134</v>
+        <v>-0.162</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0173</v>
+        <v>-0.1324</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7961</v>
+        <v>-0.0297</v>
       </c>
       <c r="V4" t="n">
-        <v>4.3313</v>
+        <v>-1.506</v>
       </c>
       <c r="W4" t="n">
-        <v>3.6716</v>
+        <v>0.2821</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6597</v>
+        <v>-1.788</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. FRANCES PASCUAL</t>
+          <t>V. ALONSO PASCUAL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7104</v>
+        <v>1.1965</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4304</v>
+        <v>0.13</v>
       </c>
       <c r="F5" t="n">
-        <v>0.28</v>
+        <v>1.0665</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4197</v>
+        <v>0.0153</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5643</v>
+        <v>-1.2259</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1446</v>
+        <v>1.2413</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7209</v>
+        <v>0.7857</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7209</v>
+        <v>-0.4778</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.2635</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3011</v>
+        <v>-0.7704</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1565</v>
+        <v>-0.7481</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1446</v>
+        <v>-0.0223</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1642</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1642</v>
+        <v>1.7463</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3093</v>
+        <v>-0.48</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2905</v>
+        <v>-0.1929</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0188</v>
+        <v>-0.2871</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5642</v>
+        <v>2.8254</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.4477</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5642</v>
+        <v>0.3776</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V. ALONSO PASCUAL</t>
+          <t>J. FRANCES PASCUAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.572</v>
+        <v>0.9379</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3309</v>
+        <v>0.6306</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9029</v>
+        <v>0.3073</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0153</v>
+        <v>0.4197</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2259</v>
+        <v>0.5643</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2413</v>
+        <v>-0.1446</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7857</v>
+        <v>0.7209</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.4778</v>
+        <v>0.7209</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2635</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7704</v>
+        <v>-0.3011</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7481</v>
+        <v>-0.1565</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0223</v>
+        <v>-0.1446</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1642</v>
+        <v>1.1642</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7463</v>
+        <v>1.1642</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1045</v>
+        <v>-0.0819</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6539</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4506</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>2.8254</v>
+        <v>-0.5642</v>
       </c>
       <c r="W6" t="n">
-        <v>2.4477</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3776</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. GUEYE</t>
+          <t>D. LORENZO  NEGRETE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0849</v>
+        <v>0.0437</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2674</v>
+        <v>-1.1351</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3523</v>
+        <v>1.1788</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08260000000000001</v>
+        <v>1.5698</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.0061</v>
+        <v>-1.1213</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0888</v>
+        <v>2.6911</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0478</v>
+        <v>1.0211</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2513</v>
+        <v>-0.8692</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2991</v>
+        <v>1.8903</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9651999999999999</v>
+        <v>0.5487</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7549</v>
+        <v>-0.2521</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7897</v>
+        <v>0.8008</v>
       </c>
       <c r="P7" t="n">
-        <v>0.194</v>
+        <v>-2.3284</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9403</v>
+        <v>-3.8806</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1344</v>
+        <v>1.5523</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5157</v>
+        <v>0.1904</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4385</v>
+        <v>-0.1113</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0772</v>
+        <v>0.3017</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7075</v>
+        <v>0.6119</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1865</v>
+        <v>1.8358</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.894</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. LORENZO  NEGRETE</t>
+          <t>C. KLOTZ MAROTO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009900000000000001</v>
+        <v>-0.1248</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4959</v>
+        <v>-3.3017</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5058</v>
+        <v>3.1769</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5698</v>
+        <v>1.1838</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1213</v>
+        <v>-1.52</v>
       </c>
       <c r="I8" t="n">
-        <v>2.6911</v>
+        <v>2.7038</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0211</v>
+        <v>0.1239</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8692</v>
+        <v>-1.2564</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8903</v>
+        <v>1.3803</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5487</v>
+        <v>1.0599</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2521</v>
+        <v>-0.2637</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8008</v>
+        <v>1.3235</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.3284</v>
+        <v>-1.5523</v>
       </c>
       <c r="Q8" t="n">
         <v>-3.8806</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5523</v>
+        <v>2.3284</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1566</v>
+        <v>-0.6982</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4722</v>
+        <v>-0.7689</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6288</v>
+        <v>0.0707</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6119</v>
+        <v>0.9418</v>
       </c>
       <c r="W8" t="n">
-        <v>1.8358</v>
+        <v>1.2239</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2239</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. KLOTZ MAROTO</t>
+          <t>B. GUEYE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7732</v>
+        <v>-0.5825</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.623</v>
+        <v>-0.9076</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8498</v>
+        <v>0.3251</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1838</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.52</v>
+        <v>-2.0061</v>
       </c>
       <c r="I9" t="n">
-        <v>2.7038</v>
+        <v>2.0888</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1239</v>
+        <v>1.0478</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2564</v>
+        <v>-0.2513</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3803</v>
+        <v>1.2991</v>
       </c>
       <c r="M9" t="n">
-        <v>1.0599</v>
+        <v>-0.9651999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2637</v>
+        <v>-1.7549</v>
       </c>
       <c r="O9" t="n">
-        <v>1.3235</v>
+        <v>0.7897</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.5523</v>
+        <v>0.194</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.8806</v>
+        <v>-1.9403</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3284</v>
+        <v>2.1344</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3466</v>
+        <v>-0.1517</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0902</v>
+        <v>-0.2016</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2564</v>
+        <v>0.0499</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9418</v>
+        <v>-0.7075</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2239</v>
+        <v>0.1865</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2821</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6118</v>
+        <v>-3.0395</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7289</v>
+        <v>-1.1293</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8829</v>
+        <v>-1.9102</v>
       </c>
       <c r="G10" t="n">
         <v>-0.067</v>
@@ -1234,13 +1234,13 @@
         <v>0.7761</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4551</v>
+        <v>0.0275</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2434</v>
+        <v>-0.157</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2118</v>
+        <v>0.1845</v>
       </c>
       <c r="V10" t="n">
         <v>-1.8358</v>
@@ -1267,19 +1267,19 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>15.3327</v>
+        <v>15.9382</v>
       </c>
       <c r="E11" t="n">
-        <v>3.9951</v>
+        <v>4.6006</v>
       </c>
       <c r="F11" t="n">
-        <v>11.3374</v>
+        <v>11.3378</v>
       </c>
       <c r="G11" t="n">
         <v>12.3723</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3048999999999993</v>
+        <v>0.3049000000000002</v>
       </c>
       <c r="I11" t="n">
         <v>12.0678</v>
@@ -1288,10 +1288,10 @@
         <v>12.3933</v>
       </c>
       <c r="K11" t="n">
-        <v>5.5529</v>
+        <v>5.552899999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>6.840399999999999</v>
+        <v>6.8404</v>
       </c>
       <c r="M11" t="n">
         <v>-0.02099999999999969</v>
@@ -1300,7 +1300,7 @@
         <v>-5.2483</v>
       </c>
       <c r="O11" t="n">
-        <v>5.227199999999999</v>
+        <v>5.2272</v>
       </c>
       <c r="P11" t="n">
         <v>-1.9404</v>
@@ -1312,13 +1312,13 @@
         <v>16.4928</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.916</v>
+        <v>-2.3103</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.5668</v>
+        <v>-2.9611</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6508</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>7.816299999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.202</v>
+        <v>2.2659</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5521</v>
+        <v>2.7523</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3501</v>
+        <v>-0.4863</v>
       </c>
       <c r="G12" t="n">
         <v>3.0699</v>
@@ -1390,13 +1390,13 @@
         <v>2.7164</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4183</v>
+        <v>0.4823</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4229</v>
+        <v>-0.2227</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8411999999999999</v>
+        <v>0.7049</v>
       </c>
       <c r="V12" t="n">
         <v>-2.0624</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. SÁNCHEZ FRESNILLO</t>
+          <t>J. TRUJILLO FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.6062</v>
+        <v>1.4987</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6682</v>
+        <v>-0.1742</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.062</v>
+        <v>1.6729</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4711</v>
+        <v>0.1805</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1229</v>
+        <v>-0.1153</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3481</v>
+        <v>0.2959</v>
       </c>
       <c r="J13" t="n">
-        <v>1.0822</v>
+        <v>0.9107</v>
       </c>
       <c r="K13" t="n">
-        <v>1.001</v>
+        <v>0.1977</v>
       </c>
       <c r="L13" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.713</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3889</v>
+        <v>-0.7302</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1219</v>
+        <v>-0.3131</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2669</v>
+        <v>-0.4171</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9702</v>
+        <v>0.194</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9702</v>
+        <v>2.1344</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2855</v>
+        <v>0.0791</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3039</v>
+        <v>-0.3685</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0184</v>
+        <v>0.4475</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.1206</v>
+        <v>1.0451</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2821</v>
+        <v>1.2239</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.4027</v>
+        <v>-0.1788</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. SAEZ BENITO</t>
+          <t>D. SÁNCHEZ FRESNILLO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8023</v>
+        <v>1.4877</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0911</v>
+        <v>1.468</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7111</v>
+        <v>0.0197</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6592</v>
+        <v>1.4711</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.781</v>
+        <v>1.1229</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1218</v>
+        <v>0.3481</v>
       </c>
       <c r="J14" t="n">
-        <v>0.07099999999999999</v>
+        <v>1.0822</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6014</v>
+        <v>1.001</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6724</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7302</v>
+        <v>0.3889</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1796</v>
+        <v>0.1219</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5506</v>
+        <v>0.2669</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7463</v>
+        <v>0.9702</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7463</v>
+        <v>0.9702</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1761</v>
+        <v>0.1671</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.544</v>
+        <v>0.1037</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7201</v>
+        <v>0.0634</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.4609</v>
+        <v>-1.1206</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5642</v>
+        <v>0.2821</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.025</v>
+        <v>-1.4027</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. TRUJILLO FERNÁNDEZ</t>
+          <t>G. PACHECO TABERNERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7891</v>
+        <v>0.8269</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.7748</v>
+        <v>0.3287</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5639</v>
+        <v>0.4982</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1805</v>
+        <v>0.4505</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1153</v>
+        <v>-0.0017</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2959</v>
+        <v>0.4521</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9107</v>
+        <v>0.6736</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1977</v>
+        <v>0.0824</v>
       </c>
       <c r="L15" t="n">
-        <v>0.713</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7302</v>
+        <v>-0.2231</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3131</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4171</v>
+        <v>-0.139</v>
       </c>
       <c r="P15" t="n">
-        <v>0.194</v>
+        <v>0.7761</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1344</v>
+        <v>0.7761</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.221</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9691</v>
+        <v>-0.3449</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3385</v>
+        <v>0.1239</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0451</v>
+        <v>-0.1788</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>-0.1788</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. PACHECO TABERNERO</t>
+          <t>J. SAEZ BENITO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6539</v>
+        <v>0.7661</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1285</v>
+        <v>0.1912</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5254</v>
+        <v>0.5748</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4505</v>
+        <v>-0.6592</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0017</v>
+        <v>-0.781</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4521</v>
+        <v>0.1218</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6736</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0824</v>
+        <v>-0.6014</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5911999999999999</v>
+        <v>0.6724</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2231</v>
+        <v>-0.7302</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.1796</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.139</v>
+        <v>-0.5506</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7761</v>
+        <v>1.7463</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7761</v>
+        <v>1.7463</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3939</v>
+        <v>0.1399</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5451</v>
+        <v>-0.4439</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1512</v>
+        <v>0.5838</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1788</v>
+        <v>-0.4609</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.5642</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1788</v>
+        <v>-1.025</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.907</v>
+        <v>-0.6462</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7103</v>
+        <v>-1.6102</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8033</v>
+        <v>0.964</v>
       </c>
       <c r="G17" t="n">
         <v>-0.408</v>
@@ -1780,13 +1780,13 @@
         <v>2.1344</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0428</v>
+        <v>0.3037</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2412</v>
+        <v>-0.1411</v>
       </c>
       <c r="U17" t="n">
-        <v>0.284</v>
+        <v>0.4447</v>
       </c>
       <c r="V17" t="n">
         <v>0.2343</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. SANTAMARIA LEON</t>
+          <t>L. BERMEJO ALCALDE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6637</v>
+        <v>-2.2209</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0975</v>
+        <v>-1.2395</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.7611</v>
+        <v>-0.9814000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.463</v>
+        <v>-2.1256</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1326</v>
+        <v>-1.3487</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3303</v>
+        <v>-0.7769</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4561</v>
+        <v>-0.4496</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3749</v>
+        <v>-0.4902</v>
       </c>
       <c r="L18" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.0406</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9191</v>
+        <v>-1.676</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5075</v>
+        <v>-0.8585</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4115</v>
+        <v>-0.8175</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9702</v>
+        <v>0.7761</v>
       </c>
       <c r="Q18" t="n">
+        <v>-0.9702</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.7463</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.1803</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.1722</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-1.2239</v>
+      </c>
+      <c r="W18" t="n">
         <v>0</v>
       </c>
-      <c r="R18" t="n">
-        <v>0.9702</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.6068</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.9713000000000001</v>
-      </c>
-      <c r="U18" t="n">
-        <v>-0.3645</v>
-      </c>
-      <c r="V18" t="n">
-        <v>-2.7776</v>
-      </c>
-      <c r="W18" t="n">
-        <v>-0.3299</v>
-      </c>
       <c r="X18" t="n">
-        <v>-2.4477</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8341</v>
+        <v>-2.3074</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.5278</v>
+        <v>-3.0283</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6937</v>
+        <v>0.721</v>
       </c>
       <c r="G19" t="n">
         <v>-2.693</v>
@@ -1936,13 +1936,13 @@
         <v>1.5523</v>
       </c>
       <c r="S19" t="n">
-        <v>1.5962</v>
+        <v>1.123</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8512</v>
+        <v>0.3507</v>
       </c>
       <c r="U19" t="n">
-        <v>0.745</v>
+        <v>0.7722</v>
       </c>
       <c r="V19" t="n">
         <v>-1.3194</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. BERMEJO ALCALDE</t>
+          <t>F. SANTAMARIA LEON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8454</v>
+        <v>-2.331</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5398</v>
+        <v>0.2967</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3057</v>
+        <v>-2.6277</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.1256</v>
+        <v>-0.463</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3487</v>
+        <v>-0.1326</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7769</v>
+        <v>-0.3303</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4496</v>
+        <v>0.4561</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4902</v>
+        <v>0.3749</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0406</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.676</v>
+        <v>-0.9191</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8585</v>
+        <v>-0.5075</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8175</v>
+        <v>-0.4115</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7761</v>
+        <v>0.9702</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7463</v>
+        <v>0.9702</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2721</v>
+        <v>-0.0606</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.12</v>
+        <v>0.1705</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1521</v>
+        <v>-0.231</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2239</v>
+        <v>-2.7776</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.3299</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2239</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6933</v>
+        <v>-3.542</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4513</v>
+        <v>-0.6515</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.2421</v>
+        <v>-2.8906</v>
       </c>
       <c r="G21" t="n">
         <v>-4.1039</v>
@@ -2092,13 +2092,13 @@
         <v>1.5523</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1106</v>
+        <v>0.2619</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3656</v>
+        <v>0.1654</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.255</v>
+        <v>0.0965</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2821</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.0548</v>
+        <v>-4.9209</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.1311</v>
+        <v>-3.8308</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9237</v>
+        <v>-1.0901</v>
       </c>
       <c r="G22" t="n">
         <v>-4.0693</v>
@@ -2170,13 +2170,13 @@
         <v>1.3582</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2847</v>
+        <v>0.4186</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4229</v>
+        <v>-0.1226</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7075</v>
+        <v>0.5412</v>
       </c>
       <c r="V22" t="n">
         <v>0.2821</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.3876</v>
+        <v>-5.5422</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.7398</v>
+        <v>-5.8399</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3522</v>
+        <v>0.2977</v>
       </c>
       <c r="G23" t="n">
         <v>-3.0224</v>
@@ -2248,13 +2248,13 @@
         <v>0.7761</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6916</v>
+        <v>0.5369</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1222</v>
+        <v>0.0221</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5693</v>
+        <v>0.5148</v>
       </c>
       <c r="V23" t="n">
         <v>0.0478</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-15.3324</v>
+        <v>-14.6653</v>
       </c>
       <c r="E24" t="n">
         <v>-11.3375</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.995100000000001</v>
+        <v>-3.3278</v>
       </c>
       <c r="G24" t="n">
         <v>-12.3724</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3048000000000007</v>
+        <v>-0.3047999999999998</v>
       </c>
       <c r="I24" t="n">
         <v>-12.0675</v>
@@ -2317,7 +2317,7 @@
         <v>-6.840199999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>1.940299999999999</v>
+        <v>1.940300000000001</v>
       </c>
       <c r="Q24" t="n">
         <v>-16.4928</v>
@@ -2326,16 +2326,16 @@
         <v>18.4332</v>
       </c>
       <c r="S24" t="n">
-        <v>2.9161</v>
+        <v>3.5833</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6510000000000001</v>
+        <v>-0.6509999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>3.5668</v>
+        <v>4.2341</v>
       </c>
       <c r="V24" t="n">
-        <v>-7.816399999999999</v>
+        <v>-7.816400000000001</v>
       </c>
       <c r="W24" t="n">
         <v>5.785</v>
